--- a/Monthly_Budgeting_Forecasting/Monthly_Budget_Forecasting_Tool.xlsx
+++ b/Monthly_Budgeting_Forecasting/Monthly_Budget_Forecasting_Tool.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Documents\GitHub\Financial-Analysis-Portfolio\Monthly_Budgeting_Forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A16AAD6-907A-4213-BC67-F1B6A168656D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A685FA23-A505-4D7E-BE8F-481D1D1842B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Actual Expenses" sheetId="6" r:id="rId1"/>
-    <sheet name="Forecast" sheetId="5" r:id="rId2"/>
-    <sheet name="Live Denamic" sheetId="4" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="3" r:id="rId4"/>
+    <sheet name="Cover" sheetId="7" r:id="rId1"/>
+    <sheet name="Actual Expenses" sheetId="6" r:id="rId2"/>
+    <sheet name="Forecast" sheetId="5" r:id="rId3"/>
+    <sheet name="Live Dynamic" sheetId="4" r:id="rId4"/>
+    <sheet name="Income Statement" sheetId="3" r:id="rId5"/>
+    <sheet name="__tracelight_scratchpad__" sheetId="8" state="veryHidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="66">
   <si>
     <t>Tax Rate</t>
   </si>
@@ -92,9 +94,6 @@
   </si>
   <si>
     <t>Customer Acquisition Cost</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -201,18 +200,79 @@
   <si>
     <t>Start Date</t>
   </si>
+  <si>
+    <t>MONTHLY BUDGET &amp; FORECASTING TOOL</t>
+  </si>
+  <si>
+    <t>Actual Expenses</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Confidential | Internal planning use</t>
+  </si>
+  <si>
+    <t>Prepared by Mohamed Magdy | mohamedeones123@gmail.com</t>
+  </si>
+  <si>
+    <t>QUICK LINKS</t>
+  </si>
+  <si>
+    <t>ONLINE PROFILES</t>
+  </si>
+  <si>
+    <t>MODEL SNAPSHOT</t>
+  </si>
+  <si>
+    <t>Start date</t>
+  </si>
+  <si>
+    <t>Forecast end</t>
+  </si>
+  <si>
+    <t>KEY ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>Executive planning dashboard | Actuals, forecasts, and management reporting</t>
+  </si>
+  <si>
+    <t>Operating Income</t>
+  </si>
+  <si>
+    <t>Forecast months</t>
+  </si>
+  <si>
+    <t>Base price</t>
+  </si>
+  <si>
+    <t>COGS % Rev.</t>
+  </si>
+  <si>
+    <t>Income Stmt.</t>
+  </si>
+  <si>
+    <t>Live Dynamic</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="[$$-C09]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="[$$-C09]#,##0"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,8 +401,132 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF073673"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF073673"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0432FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0432FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0432FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,8 +605,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -483,6 +685,148 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -490,7 +834,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -574,6 +918,257 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="29" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="29" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="17" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="25" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="25" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
@@ -597,6 +1192,1135 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue &amp; Net Income Trend</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="073673"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="073673"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="073673"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Income Statement'!$C$5:$N$5</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>46413</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46444</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46472</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46503</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46533</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46564</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46594</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46656</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46686</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46717</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46747</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Income Statement'!$C$6:$N$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>441690.11119911837</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>434633.26649093837</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>434024.73711992078</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>426374.80021809932</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>425675.84223428363</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>418665.41351978196</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>559567.36056209577</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>550452.01502729836</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>547647.06153050903</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>538096.86712310871</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>536833.94834782719</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>526347.30762897921</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D428-4A01-A7BD-67AF7AC7AC48}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1757407744"/>
+        <c:axId val="1776801472"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Net Income</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Income Statement'!$C$22:$N$22</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>42335.734807481684</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38697.852680316486</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37124.417638208753</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33391.200468175361</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31942.555164825731</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28729.534831102588</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>111539.51361909442</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106702.8272978975</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>104365.42417939776</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99537.439918617747</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97496.515006091387</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>92056.665419168115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D428-4A01-A7BD-67AF7AC7AC48}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1854965216"/>
+        <c:axId val="1776823072"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1757407744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mmm\-yy" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-2700000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="2E2E38"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1776801472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1776801472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="600000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="2E2E38"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757407744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1776823072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="\$#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1854965216"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1854965216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1776823072"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="tracelight-8f91af0d06394755revenue-vs-net-income">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDF791C6-DD54-B8B2-4B97-EEF19FD717C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,7 +2584,383 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{20327D53-632D-4007-9E18-5136D6970A5C}">
+  <we:reference id="wa200008399" version="1.0.0.5" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200008399" version="1.0.0.5" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="ProjectMetadata" value="&quot;{\&quot;projectId\&quot;:\&quot;cf6330a6-5c50-4c03-9efa-87725544d110\&quot;}&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B50C841-616D-4B49-A3EA-670FD7C60B59}">
+  <sheetPr>
+    <tabColor rgb="FF073673"/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="9" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="49"/>
+      <c r="B2" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+    </row>
+    <row r="3" spans="1:9" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="49"/>
+      <c r="B3" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+    </row>
+    <row r="4" spans="1:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+    </row>
+    <row r="6" spans="1:9" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+    </row>
+    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="49"/>
+      <c r="B7" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="118"/>
+      <c r="D7" s="120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="118"/>
+      <c r="F7" s="120" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="118"/>
+      <c r="H7" s="120" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="122"/>
+    </row>
+    <row r="8" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="49"/>
+      <c r="B8" s="121">
+        <f>'Income Statement'!C6</f>
+        <v>441690.11119911837</v>
+      </c>
+      <c r="C8" s="119"/>
+      <c r="D8" s="121">
+        <f>'Income Statement'!C8</f>
+        <v>353352.08895929472</v>
+      </c>
+      <c r="E8" s="119"/>
+      <c r="F8" s="121">
+        <f>'Income Statement'!C16</f>
+        <v>58656.09696597117</v>
+      </c>
+      <c r="G8" s="119"/>
+      <c r="H8" s="121">
+        <f>'Income Statement'!C22</f>
+        <v>42335.734807481684</v>
+      </c>
+      <c r="I8" s="123"/>
+    </row>
+    <row r="9" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="49"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+    </row>
+    <row r="10" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="49"/>
+      <c r="B10" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="124"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="74"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="74"/>
+    </row>
+    <row r="11" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="49"/>
+      <c r="B11" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="125">
+        <f>'Actual Expenses'!C2</f>
+        <v>46291</v>
+      </c>
+      <c r="D11" s="111"/>
+      <c r="E11" s="82" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="127">
+        <f>'Income Statement'!C40</f>
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="111"/>
+      <c r="H11" s="82" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="129" t="str">
+        <f>HYPERLINK("#'Actual Expenses'!A1","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="49"/>
+      <c r="B12" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="125">
+        <f>'Income Statement'!N5</f>
+        <v>46747</v>
+      </c>
+      <c r="D12" s="111"/>
+      <c r="E12" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="127">
+        <f>'Income Statement'!C34</f>
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="111"/>
+      <c r="H12" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="129" t="str">
+        <f>HYPERLINK("#Forecast!A1","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="49"/>
+      <c r="B13" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="126">
+        <f>COLUMNS('Income Statement'!C5:N5)</f>
+        <v>12</v>
+      </c>
+      <c r="D13" s="111"/>
+      <c r="E13" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="128">
+        <f>'Income Statement'!C28</f>
+        <v>250</v>
+      </c>
+      <c r="G13" s="111"/>
+      <c r="H13" s="82" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="129" t="str">
+        <f>HYPERLINK("#'Live Dynamic'!A1","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="49"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="129" t="str">
+        <f>HYPERLINK("#'Income Statement'!A1","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="49"/>
+      <c r="B15" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="131"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+    </row>
+    <row r="16" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="49"/>
+      <c r="B16" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="129" t="str">
+        <f>HYPERLINK("https://linkedin.com/in/mohamed-magdy-finance","LinkedIn")</f>
+        <v>LinkedIn</v>
+      </c>
+      <c r="D16" s="111"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+    </row>
+    <row r="17" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="49"/>
+      <c r="B17" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="130" t="str">
+        <f>HYPERLINK("https://github.com/Mohamed-Magdy-Finance","GitHub")</f>
+        <v>GitHub</v>
+      </c>
+      <c r="D17" s="111"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+    </row>
+    <row r="18" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="49"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+    </row>
+    <row r="19" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="49"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="111"/>
+    </row>
+    <row r="20" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="49"/>
+      <c r="B20" s="117" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+    </row>
+    <row r="21" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="49"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C278B4-4D81-444F-BDEF-8E34F6A11362}">
   <dimension ref="B2:H13"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -874,7 +2974,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="45">
         <v>46291</v>
@@ -882,7 +2982,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -893,13 +2993,13 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="17">
         <f>C2</f>
@@ -923,10 +3023,10 @@
         <v>11256</v>
       </c>
       <c r="C6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="27">
         <v>22992</v>
@@ -946,10 +3046,10 @@
         <v>11257</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="27">
         <v>53326</v>
@@ -969,10 +3069,10 @@
         <v>11259</v>
       </c>
       <c r="C8" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E8" s="27">
         <v>35888</v>
@@ -992,10 +3092,10 @@
         <v>11260</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="27">
         <v>87942</v>
@@ -1015,10 +3115,10 @@
         <v>11263</v>
       </c>
       <c r="C10" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="E10" s="27">
         <v>92622</v>
@@ -1038,10 +3138,10 @@
         <v>11264</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="27">
         <v>27416</v>
@@ -1061,10 +3161,10 @@
         <v>11267</v>
       </c>
       <c r="C12" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="28" t="s">
         <v>31</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>32</v>
       </c>
       <c r="E12" s="27">
         <v>41696</v>
@@ -1084,10 +3184,10 @@
         <v>11268</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="27">
         <v>60285</v>
@@ -1107,7 +3207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F33986-4B12-42ED-84F1-1530B745E793}">
   <dimension ref="A2:T40"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1121,18 +3221,18 @@
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
@@ -1853,7 +3953,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="46">
         <v>0.3</v>
@@ -1861,18 +3961,18 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
       <c r="E15" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -2593,7 +4693,7 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="46">
         <v>0.2</v>
@@ -2601,18 +4701,18 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
       <c r="E28" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
       <c r="I28" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
@@ -3379,7 +5479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF420EC6-DA7B-4D05-A0E6-266ED1389A60}">
   <dimension ref="A2:T42"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3395,7 +5495,7 @@
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D2" s="47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="47"/>
       <c r="F2" s="47"/>
@@ -3404,18 +5504,18 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
       <c r="I4" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
@@ -4188,7 +6288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{578FC9CE-18F0-451A-988F-3930A1516B9C}">
   <dimension ref="A2:O40"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
@@ -4201,7 +6301,7 @@
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="44">
         <v>2</v>
@@ -4212,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -4229,7 +6329,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="17">
         <f>Forecast!I3</f>
@@ -4388,7 +6488,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8" s="34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="39">
         <f t="shared" ref="C8:N8" si="2">C6-C7</f>
@@ -4456,7 +6556,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -4465,51 +6565,51 @@
         <v>Marketing</v>
       </c>
       <c r="C11" s="4">
-        <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!I$6:I$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>53002.813343894202</v>
       </c>
       <c r="D11" s="4">
-        <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!J$6:J$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>52155.9919789126</v>
       </c>
       <c r="E11" s="4">
-        <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!K$6:K$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>52082.968454390488</v>
       </c>
       <c r="F11" s="4">
-        <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!L$6:L$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>51164.97602617192</v>
       </c>
       <c r="G11" s="4">
-        <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!M$6:M$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>51081.101068114032</v>
       </c>
       <c r="H11" s="4">
-        <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!N$6:N$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>50239.849622373833</v>
       </c>
       <c r="I11" s="4">
-        <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!O$6:O$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>49961.371478758549</v>
       </c>
       <c r="J11" s="4">
-        <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!P$6:P$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>49147.501341723066</v>
       </c>
       <c r="K11" s="4">
-        <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!Q$6:Q$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>48897.059065224021</v>
       </c>
       <c r="L11" s="4">
-        <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!R$6:R$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>48044.363135991851</v>
       </c>
       <c r="M11" s="4">
-        <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!S$6:S$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>47931.602531055993</v>
       </c>
       <c r="N11" s="4">
-        <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
+        <f>SUMIFS('Live Dynamic'!T$6:T$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
         <v>46995.295324015999</v>
       </c>
       <c r="O11" s="15"/>
@@ -4519,51 +6619,51 @@
         <v>Engineering</v>
       </c>
       <c r="C12" s="4">
-        <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!I$6:I$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>83728.303927260044</v>
       </c>
       <c r="D12" s="4">
-        <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!J$6:J$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>83154.200568212254</v>
       </c>
       <c r="E12" s="4">
-        <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!K$6:K$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>82564.043030396744</v>
       </c>
       <c r="F12" s="4">
-        <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!L$6:L$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>81918.075504254797</v>
       </c>
       <c r="G12" s="4">
-        <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!M$6:M$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>81302.522334508467</v>
       </c>
       <c r="H12" s="4">
-        <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!N$6:N$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>80686.119978127914</v>
       </c>
       <c r="I12" s="4">
-        <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!O$6:O$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>80069.183756359213</v>
       </c>
       <c r="J12" s="4">
-        <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!P$6:P$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>79448.446499391081</v>
       </c>
       <c r="K12" s="4">
-        <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!Q$6:Q$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>78830.261668152554</v>
       </c>
       <c r="L12" s="4">
-        <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!R$6:R$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>78212.144645000095</v>
       </c>
       <c r="M12" s="4">
-        <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!S$6:S$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>77594.060603663922</v>
       </c>
       <c r="N12" s="4">
-        <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
+        <f>SUMIFS('Live Dynamic'!T$6:T$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
         <v>76975.985350966133</v>
       </c>
       <c r="O12" s="15"/>
@@ -4573,51 +6673,51 @@
         <v>Support</v>
       </c>
       <c r="C13" s="4">
-        <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!I$6:I$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>71891.08726384156</v>
       </c>
       <c r="D13" s="4">
-        <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!J$6:J$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>68720.942589501195</v>
       </c>
       <c r="E13" s="4">
-        <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!K$6:K$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>65535.550530007939</v>
       </c>
       <c r="F13" s="4">
-        <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!L$6:L$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>62433.672673956666</v>
       </c>
       <c r="G13" s="4">
-        <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!M$6:M$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>59297.914016999872</v>
       </c>
       <c r="H13" s="4">
-        <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!N$6:N$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>55809.215989504504</v>
       </c>
       <c r="I13" s="4">
-        <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!O$6:O$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>53101.575874364629</v>
       </c>
       <c r="J13" s="4">
-        <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!P$6:P$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>49858.469992924634</v>
       </c>
       <c r="K13" s="4">
-        <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!Q$6:Q$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>46427.196699238812</v>
       </c>
       <c r="L13" s="4">
-        <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!R$6:R$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>43635.726629039535</v>
       </c>
       <c r="M13" s="4">
-        <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!S$6:S$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>40378.091716998213</v>
       </c>
       <c r="N13" s="4">
-        <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
+        <f>SUMIFS('Live Dynamic'!T$6:T$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
         <v>36969.279376805083</v>
       </c>
       <c r="O13" s="15"/>
@@ -4627,58 +6727,58 @@
         <v>HR</v>
       </c>
       <c r="C14" s="4">
-        <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!I$6:I$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>86073.787458327773</v>
       </c>
       <c r="D14" s="4">
-        <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!J$6:J$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>89905.174816581304</v>
       </c>
       <c r="E14" s="4">
-        <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!K$6:K$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>95367.880477930186</v>
       </c>
       <c r="F14" s="4">
-        <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!L$6:L$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>98929.641344771808</v>
       </c>
       <c r="G14" s="4">
-        <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!M$6:M$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>104140.68360353216</v>
       </c>
       <c r="H14" s="4">
-        <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!N$6:N$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>107797.77171675027</v>
       </c>
       <c r="I14" s="4">
-        <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!O$6:O$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>113004.56904525784</v>
       </c>
       <c r="J14" s="4">
-        <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!P$6:P$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>116884.49771546668</v>
       </c>
       <c r="K14" s="4">
-        <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!Q$6:Q$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>122070.99757827564</v>
       </c>
       <c r="L14" s="4">
-        <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!R$6:R$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>125178.18839468292</v>
       </c>
       <c r="M14" s="4">
-        <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!S$6:S$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>130883.88074334929</v>
       </c>
       <c r="N14" s="4">
-        <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
+        <f>SUMIFS('Live Dynamic'!T$6:T$13,'Live Dynamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
         <v>134763.32895436042</v>
       </c>
       <c r="O14" s="15"/>
     </row>
     <row r="15" spans="1:15" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B15" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="40">
         <f t="shared" ref="C15:N15" si="3">SUM(C11:C14)</f>
@@ -4732,7 +6832,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="41">
         <f t="shared" ref="C16:N16" si="4">C8-C15</f>
@@ -4853,7 +6953,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B19" s="34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="39">
         <f t="shared" ref="C19:N19" si="6">C16-C18</f>
@@ -4921,7 +7021,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B21" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="42">
         <f t="shared" ref="C21:N21" si="7">C19*$C$40</f>
@@ -4974,7 +7074,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B22" s="38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="40">
         <f t="shared" ref="C22:N22" si="8">C19-C21</f>
@@ -5029,9 +7129,7 @@
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>11</v>
-      </c>
+      <c r="B25" s="14"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -5456,4 +7554,677 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50A3902-2726-4F4E-9908-4742B3CF6314}">
+  <dimension ref="A24:H115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="24" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="50"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="55"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="57"/>
+      <c r="B29" s="60"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="57"/>
+      <c r="B31" s="60"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="61"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="62"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="57"/>
+      <c r="B37" s="60"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="61"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="61"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="69"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="62"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="62"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="57"/>
+      <c r="B43" s="60"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="61"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="62"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="53"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="71"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+    </row>
+    <row r="52" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="72"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="72"/>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="73"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="58"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="51"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="58"/>
+      <c r="B56" s="75"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="76"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="59"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="51"/>
+      <c r="D57" s="76"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51"/>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="49"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="73"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="58"/>
+      <c r="B60" s="75"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="51"/>
+      <c r="G60" s="51"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="58"/>
+      <c r="B61" s="75"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="78"/>
+      <c r="G61" s="79"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="59"/>
+      <c r="B62" s="65"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="80"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="65"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="73"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="58"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="59"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="81"/>
+      <c r="B68" s="81"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="87"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="87"/>
+      <c r="E70" s="97"/>
+      <c r="F70" s="97"/>
+      <c r="G70" s="88"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="89"/>
+      <c r="B71" s="91"/>
+      <c r="C71" s="98"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="99"/>
+      <c r="F71" s="99"/>
+      <c r="G71" s="94"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="89"/>
+      <c r="B72" s="91"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="99"/>
+      <c r="F72" s="99"/>
+      <c r="G72" s="94"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="89"/>
+      <c r="B73" s="91"/>
+      <c r="C73" s="98"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="99"/>
+      <c r="F73" s="99"/>
+      <c r="G73" s="94"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="90"/>
+      <c r="B74" s="92"/>
+      <c r="C74" s="98"/>
+      <c r="D74" s="95"/>
+      <c r="E74" s="100"/>
+      <c r="F74" s="100"/>
+      <c r="G74" s="96"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="98"/>
+      <c r="B75" s="98"/>
+      <c r="C75" s="98"/>
+      <c r="D75" s="98"/>
+      <c r="E75" s="98"/>
+      <c r="F75" s="98"/>
+      <c r="G75" s="98"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="98"/>
+      <c r="B76" s="98"/>
+      <c r="C76" s="98"/>
+      <c r="D76" s="98"/>
+      <c r="E76" s="98"/>
+      <c r="F76" s="98"/>
+      <c r="G76" s="98"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="98"/>
+      <c r="B77" s="98"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="98"/>
+      <c r="E77" s="98"/>
+      <c r="F77" s="98"/>
+      <c r="G77" s="98"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="98"/>
+      <c r="B78" s="98"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="98"/>
+      <c r="E78" s="98"/>
+      <c r="F78" s="98"/>
+      <c r="G78" s="98"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="98"/>
+      <c r="B79" s="98"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="98"/>
+      <c r="E79" s="98"/>
+      <c r="F79" s="98"/>
+      <c r="G79" s="98"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="98"/>
+      <c r="B80" s="98"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="98"/>
+      <c r="E80" s="98"/>
+      <c r="F80" s="98"/>
+      <c r="G80" s="98"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="98"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="98"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="98"/>
+      <c r="B82" s="98"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="98"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="98"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="98"/>
+      <c r="B84" s="98"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="87"/>
+      <c r="E84" s="97"/>
+      <c r="F84" s="97"/>
+      <c r="G84" s="88"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="98"/>
+      <c r="B85" s="98"/>
+      <c r="C85" s="98"/>
+      <c r="D85" s="89"/>
+      <c r="E85" s="103"/>
+      <c r="F85" s="98"/>
+      <c r="G85" s="84"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="98"/>
+      <c r="B86" s="98"/>
+      <c r="C86" s="98"/>
+      <c r="D86" s="90"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="86"/>
+      <c r="G86" s="85"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="98"/>
+      <c r="B87" s="98"/>
+      <c r="C87" s="98"/>
+      <c r="D87" s="98"/>
+      <c r="E87" s="98"/>
+      <c r="F87" s="98"/>
+      <c r="G87" s="98"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="98"/>
+      <c r="B88" s="98"/>
+      <c r="C88" s="98"/>
+      <c r="D88" s="98"/>
+      <c r="E88" s="98"/>
+      <c r="F88" s="98"/>
+      <c r="G88" s="98"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="98"/>
+      <c r="B89" s="98"/>
+      <c r="C89" s="98"/>
+      <c r="D89" s="98"/>
+      <c r="E89" s="98"/>
+      <c r="F89" s="98"/>
+      <c r="G89" s="98"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="98"/>
+      <c r="B90" s="98"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="98"/>
+      <c r="E90" s="98"/>
+      <c r="F90" s="98"/>
+      <c r="G90" s="98"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="49"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49"/>
+      <c r="E92" s="49"/>
+      <c r="F92" s="49"/>
+      <c r="G92" s="49"/>
+      <c r="H92" s="49"/>
+    </row>
+    <row r="93" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="49"/>
+      <c r="B93" s="70"/>
+      <c r="C93" s="70"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+    </row>
+    <row r="94" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="49"/>
+      <c r="B94" s="71"/>
+      <c r="C94" s="71"/>
+      <c r="D94" s="71"/>
+      <c r="E94" s="71"/>
+      <c r="F94" s="71"/>
+      <c r="G94" s="71"/>
+      <c r="H94" s="71"/>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="49"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
+      <c r="D95" s="49"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+    </row>
+    <row r="96" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="49"/>
+      <c r="B96" s="72"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="72"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="72"/>
+      <c r="G96" s="72"/>
+      <c r="H96" s="72"/>
+    </row>
+    <row r="97" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="49"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49"/>
+      <c r="D97" s="49"/>
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="49"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="49"/>
+      <c r="B98" s="87"/>
+      <c r="C98" s="88"/>
+      <c r="D98" s="98"/>
+      <c r="E98" s="87"/>
+      <c r="F98" s="97"/>
+      <c r="G98" s="97"/>
+      <c r="H98" s="88"/>
+    </row>
+    <row r="99" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="49"/>
+      <c r="B99" s="89"/>
+      <c r="C99" s="101"/>
+      <c r="D99" s="98"/>
+      <c r="E99" s="89"/>
+      <c r="F99" s="103"/>
+      <c r="G99" s="98"/>
+      <c r="H99" s="84"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="49"/>
+      <c r="B100" s="89"/>
+      <c r="C100" s="101"/>
+      <c r="D100" s="98"/>
+      <c r="E100" s="89"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="98"/>
+      <c r="H100" s="84"/>
+    </row>
+    <row r="101" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="49"/>
+      <c r="B101" s="89"/>
+      <c r="C101" s="101"/>
+      <c r="D101" s="98"/>
+      <c r="E101" s="89"/>
+      <c r="F101" s="103"/>
+      <c r="G101" s="98"/>
+      <c r="H101" s="84"/>
+    </row>
+    <row r="102" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="49"/>
+      <c r="B102" s="90"/>
+      <c r="C102" s="102"/>
+      <c r="D102" s="98"/>
+      <c r="E102" s="90"/>
+      <c r="F102" s="104"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="85"/>
+    </row>
+    <row r="103" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="49"/>
+      <c r="B103" s="98"/>
+      <c r="C103" s="98"/>
+      <c r="D103" s="98"/>
+      <c r="E103" s="98"/>
+      <c r="F103" s="98"/>
+      <c r="G103" s="98"/>
+      <c r="H103" s="98"/>
+    </row>
+    <row r="104" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="49"/>
+      <c r="B104" s="87"/>
+      <c r="C104" s="88"/>
+      <c r="D104" s="98"/>
+      <c r="E104" s="87"/>
+      <c r="F104" s="97"/>
+      <c r="G104" s="97"/>
+      <c r="H104" s="88"/>
+    </row>
+    <row r="105" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="49"/>
+      <c r="B105" s="89"/>
+      <c r="C105" s="107"/>
+      <c r="D105" s="98"/>
+      <c r="E105" s="89"/>
+      <c r="F105" s="105"/>
+      <c r="G105" s="98"/>
+      <c r="H105" s="84"/>
+    </row>
+    <row r="106" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="49"/>
+      <c r="B106" s="90"/>
+      <c r="C106" s="108"/>
+      <c r="D106" s="98"/>
+      <c r="E106" s="90"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="85"/>
+    </row>
+    <row r="107" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="49"/>
+      <c r="B107" s="98"/>
+      <c r="C107" s="98"/>
+      <c r="D107" s="98"/>
+      <c r="E107" s="98"/>
+      <c r="F107" s="98"/>
+      <c r="G107" s="98"/>
+      <c r="H107" s="98"/>
+    </row>
+    <row r="108" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="49"/>
+      <c r="B108" s="87"/>
+      <c r="C108" s="88"/>
+      <c r="D108" s="98"/>
+      <c r="E108" s="98"/>
+      <c r="F108" s="98"/>
+      <c r="G108" s="98"/>
+      <c r="H108" s="98"/>
+    </row>
+    <row r="109" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="49"/>
+      <c r="B109" s="89"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="98"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="98"/>
+      <c r="H109" s="98"/>
+    </row>
+    <row r="110" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="49"/>
+      <c r="B110" s="90"/>
+      <c r="C110" s="110"/>
+      <c r="D110" s="98"/>
+      <c r="E110" s="98"/>
+      <c r="F110" s="98"/>
+      <c r="G110" s="98"/>
+      <c r="H110" s="98"/>
+    </row>
+    <row r="111" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="73"/>
+      <c r="B113" s="132"/>
+      <c r="C113" s="115"/>
+      <c r="D113" s="115"/>
+      <c r="E113" s="74"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="133"/>
+      <c r="B114" s="116"/>
+      <c r="C114" s="116"/>
+      <c r="D114" s="116"/>
+      <c r="E114" s="134"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="136"/>
+      <c r="B115" s="135"/>
+      <c r="C115" s="135"/>
+      <c r="D115" s="135"/>
+      <c r="E115" s="137"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>